--- a/artfynd/A 38921-2019 artfynd.xlsx
+++ b/artfynd/A 38921-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1095,6 +1095,146 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>69369333</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56133</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på determinatörs verifiering</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med heterodyn</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gnöst, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>526595</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6396104</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rumskulla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-08-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-08-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gles granskog NV om byn</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>

--- a/artfynd/A 38921-2019 artfynd.xlsx
+++ b/artfynd/A 38921-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
